--- a/resource/管道外径壁厚表.xlsx
+++ b/resource/管道外径壁厚表.xlsx
@@ -27,7 +27,7 @@
     <t>i</t>
   </si>
   <si>
-    <t>j</t>
+    <t>l</t>
   </si>
   <si>
     <t>10.3x2.41</t>
